--- a/data/trans_dic/P62-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,97; 83,99</t>
+          <t>68,56; 83,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,05; 61,7</t>
+          <t>43,32; 62,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,45; 73,29</t>
+          <t>57,79; 73,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,03; 74,78</t>
+          <t>59,32; 74,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,27; 57,01</t>
+          <t>36,07; 57,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,1; 41,01</t>
+          <t>23,42; 40,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,68; 47,96</t>
+          <t>29,54; 48,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,54; 57,12</t>
+          <t>42,82; 56,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,42; 69,94</t>
+          <t>55,83; 69,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,18; 49,56</t>
+          <t>36,38; 49,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,92; 58,76</t>
+          <t>46,74; 58,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,04; 64,49</t>
+          <t>53,84; 64,62</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,27; 88,3</t>
+          <t>71,45; 87,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,35; 67,72</t>
+          <t>51,33; 67,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,18; 67,48</t>
+          <t>50,94; 68,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,53; 79,89</t>
+          <t>65,76; 79,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,22; 26,54</t>
+          <t>12,31; 26,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,79; 29,96</t>
+          <t>15,99; 30,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,91; 29,06</t>
+          <t>14,94; 27,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,48; 53,92</t>
+          <t>40,29; 54,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,52; 50,7</t>
+          <t>37,48; 51,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,03; 46,77</t>
+          <t>34,73; 47,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,1; 43,02</t>
+          <t>32,2; 43,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,24; 66,28</t>
+          <t>55,99; 66,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,49; 80,01</t>
+          <t>66,27; 80,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,17; 58,32</t>
+          <t>47,78; 58,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,14; 63,32</t>
+          <t>52,58; 64,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,41; 79,16</t>
+          <t>66,4; 79,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,9; 27,29</t>
+          <t>13,34; 28,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,15; 49,3</t>
+          <t>32,77; 49,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,14; 60,15</t>
+          <t>39,74; 60,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 62,55</t>
+          <t>46,51; 62,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,62; 57,95</t>
+          <t>45,29; 57,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,82; 54,21</t>
+          <t>44,83; 54,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,92; 60,99</t>
+          <t>50,74; 60,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62,13; 72,03</t>
+          <t>61,76; 71,9</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,6; 73,14</t>
+          <t>64,5; 72,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,65; 52,57</t>
+          <t>44,55; 52,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,54; 56,88</t>
+          <t>48,75; 56,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,44; 67,09</t>
+          <t>56,36; 67,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,47; 32,4</t>
+          <t>23,31; 32,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,63; 29,74</t>
+          <t>21,18; 29,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 36,75</t>
+          <t>27,91; 36,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,76; 85,34</t>
+          <t>35,58; 84,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,69; 54,22</t>
+          <t>47,91; 54,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,55; 42,12</t>
+          <t>36,59; 42,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,3; 47,4</t>
+          <t>41,09; 47,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,5; 79,61</t>
+          <t>50,46; 79,67</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,68; 59,21</t>
+          <t>43,3; 58,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,13; 48,01</t>
+          <t>37,31; 48,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,59; 50,55</t>
+          <t>40,43; 50,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53,45; 66,43</t>
+          <t>54,26; 66,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,73; 33,68</t>
+          <t>23,54; 33,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,17; 43,41</t>
+          <t>34,97; 43,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,88; 43,41</t>
+          <t>34,9; 43,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,09; 51,25</t>
+          <t>44,06; 51,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,78; 40,49</t>
+          <t>31,35; 39,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,18; 43,91</t>
+          <t>37,21; 43,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38,65; 44,83</t>
+          <t>38,8; 45,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,93; 55,29</t>
+          <t>48,59; 55,07</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,34</t>
+          <t>1,81; 6,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 10,31</t>
+          <t>3,63; 10,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,77</t>
+          <t>1,51; 5,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,35</t>
+          <t>2,41; 8,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,7; 24,25</t>
+          <t>19,68; 24,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,04; 27,47</t>
+          <t>21,82; 27,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,56; 26,41</t>
+          <t>21,1; 26,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,52; 29,06</t>
+          <t>23,44; 29,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,45; 20,45</t>
+          <t>16,55; 20,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,96; 23,37</t>
+          <t>18,92; 23,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,84</t>
+          <t>17,12; 22,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 23,14</t>
+          <t>18,88; 23,41</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,86; 57,36</t>
+          <t>51,97; 57,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,82; 46,38</t>
+          <t>41,49; 46,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,01; 48,62</t>
+          <t>44,15; 48,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,0; 58,48</t>
+          <t>52,21; 58,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,95; 26,32</t>
+          <t>23,03; 26,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,27; 30,87</t>
+          <t>27,32; 31,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,27; 32,13</t>
+          <t>28,18; 32,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,04; 59,8</t>
+          <t>37,17; 59,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,97; 37,21</t>
+          <t>34,14; 37,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34,17; 37,08</t>
+          <t>34,13; 37,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35,9; 38,89</t>
+          <t>35,77; 38,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,79; 57,95</t>
+          <t>44,64; 60,09</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76939; 96497</t>
+          <t>78764; 96407</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56962; 81640</t>
+          <t>57317; 82126</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84359; 109526</t>
+          <t>86363; 109841</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90499; 114642</t>
+          <t>90941; 114751</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32475; 51042</t>
+          <t>32297; 51438</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27497; 48808</t>
+          <t>27874; 48084</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38746; 62611</t>
+          <t>38563; 62930</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55290; 74233</t>
+          <t>55651; 74030</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113293; 142974</t>
+          <t>114124; 142799</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90928; 124576</t>
+          <t>91427; 125193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>131380; 164529</t>
+          <t>130865; 164365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>153068; 182670</t>
+          <t>152515; 183052</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69506; 84924</t>
+          <t>68722; 84200</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82310; 108552</t>
+          <t>82283; 108065</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68163; 89876</t>
+          <t>67848; 90909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98362; 118110</t>
+          <t>97223; 117378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16874; 36648</t>
+          <t>16991; 36274</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26363; 50033</t>
+          <t>26702; 50597</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28820; 52643</t>
+          <t>27057; 50066</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51931; 69175</t>
+          <t>51691; 69729</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87892; 118775</t>
+          <t>87811; 119951</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>114636; 153075</t>
+          <t>113662; 154011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100919; 135237</t>
+          <t>101225; 135795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>155293; 183004</t>
+          <t>154603; 183148</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>106659; 128342</t>
+          <t>106298; 128777</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>164528; 203445</t>
+          <t>166652; 204788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>157458; 191200</t>
+          <t>158769; 194232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>120383; 141369</t>
+          <t>118570; 141201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14082; 29790</t>
+          <t>14560; 30578</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48245; 71758</t>
+          <t>47696; 72595</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38321; 58888</t>
+          <t>38905; 59531</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43815; 58612</t>
+          <t>43580; 58945</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>122982; 156209</t>
+          <t>122096; 154406</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221572; 268002</t>
+          <t>221637; 267624</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203600; 243859</t>
+          <t>202887; 243026</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>169159; 196128</t>
+          <t>168151; 195755</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>340610; 385640</t>
+          <t>340102; 383378</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>322205; 379375</t>
+          <t>321508; 378406</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>319132; 373983</t>
+          <t>320508; 371897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>267444; 317937</t>
+          <t>267062; 319316</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95132; 131337</t>
+          <t>94505; 131149</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95048; 136989</t>
+          <t>97570; 136997</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>126740; 166562</t>
+          <t>126495; 166693</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>197230; 470614</t>
+          <t>196225; 464392</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>444814; 505700</t>
+          <t>446854; 505976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>432104; 497962</t>
+          <t>432550; 502291</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>458735; 526473</t>
+          <t>456380; 523263</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>517767; 816298</t>
+          <t>517364; 816872</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>71098; 96394</t>
+          <t>70483; 95050</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>135663; 170806</t>
+          <t>132728; 171607</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172474; 214768</t>
+          <t>171762; 213255</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125501; 155972</t>
+          <t>127406; 155272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84341; 119697</t>
+          <t>83668; 119953</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>202999; 250550</t>
+          <t>201841; 249873</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>186697; 232363</t>
+          <t>186807; 232036</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>204906; 238186</t>
+          <t>204774; 238951</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164691; 209823</t>
+          <t>162471; 205552</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>346899; 409667</t>
+          <t>347177; 408473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>371121; 430419</t>
+          <t>372513; 434095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>342313; 386761</t>
+          <t>339894; 385213</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4876; 18699</t>
+          <t>5350; 17974</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9008; 26771</t>
+          <t>9418; 26435</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3996; 15773</t>
+          <t>4139; 16121</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5570; 19856</t>
+          <t>5735; 19412</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>245822; 302654</t>
+          <t>245619; 305757</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>242457; 302147</t>
+          <t>239975; 298189</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>216539; 278178</t>
+          <t>222264; 279182</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>177961; 219885</t>
+          <t>177384; 219656</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>253743; 315559</t>
+          <t>255342; 315866</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257775; 317744</t>
+          <t>257216; 318287</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>227106; 289774</t>
+          <t>227096; 291871</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>186751; 230078</t>
+          <t>187757; 232850</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>703479; 778050</t>
+          <t>704938; 775899</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>827474; 917680</t>
+          <t>820807; 915912</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>853951; 943303</t>
+          <t>856629; 942165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>741598; 833951</t>
+          <t>744637; 837099</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>538352; 617338</t>
+          <t>540050; 621747</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>700615; 793232</t>
+          <t>701867; 797363</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>693042; 787518</t>
+          <t>690713; 787195</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>786978; 1270673</t>
+          <t>789798; 1265640</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1257545; 1377472</t>
+          <t>1263898; 1378509</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1553842; 1686184</t>
+          <t>1552310; 1687256</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1576513; 1707991</t>
+          <t>1570645; 1696451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1590579; 2057706</t>
+          <t>1585293; 2133940</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,56; 83,91</t>
+          <t>68,25; 84,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,32; 62,06</t>
+          <t>43,92; 61,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,79; 73,5</t>
+          <t>57,77; 73,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,32; 74,85</t>
+          <t>62,86; 76,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,07; 57,45</t>
+          <t>36,0; 56,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,42; 40,4</t>
+          <t>23,15; 41,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,54; 48,2</t>
+          <t>28,88; 47,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,82; 56,96</t>
+          <t>41,85; 55,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,83; 69,85</t>
+          <t>56,06; 69,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,38; 49,81</t>
+          <t>35,7; 49,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,74; 58,7</t>
+          <t>46,83; 58,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,84; 64,62</t>
+          <t>55,43; 65,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,45; 87,55</t>
+          <t>71,58; 87,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,33; 67,41</t>
+          <t>51,37; 68,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,94; 68,25</t>
+          <t>50,02; 67,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,76; 79,4</t>
+          <t>65,46; 78,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 26,27</t>
+          <t>12,27; 26,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 30,3</t>
+          <t>16,07; 30,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 27,64</t>
+          <t>15,17; 28,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,29; 54,35</t>
+          <t>40,48; 53,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,48; 51,21</t>
+          <t>38,03; 51,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,73; 47,06</t>
+          <t>34,58; 46,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,2; 43,2</t>
+          <t>32,05; 43,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,99; 66,33</t>
+          <t>55,71; 65,88</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,27; 80,28</t>
+          <t>66,33; 79,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,78; 58,71</t>
+          <t>47,19; 58,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,58; 64,32</t>
+          <t>52,05; 63,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66,4; 79,07</t>
+          <t>65,54; 78,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 28,01</t>
+          <t>12,71; 27,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 49,87</t>
+          <t>32,38; 49,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,74; 60,81</t>
+          <t>40,37; 60,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,51; 62,91</t>
+          <t>46,56; 62,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,29; 57,28</t>
+          <t>45,75; 58,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,83; 54,13</t>
+          <t>44,85; 54,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,74; 60,78</t>
+          <t>50,9; 60,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,76; 71,9</t>
+          <t>61,0; 70,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,5; 72,71</t>
+          <t>64,53; 72,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,55; 52,44</t>
+          <t>44,83; 52,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,75; 56,56</t>
+          <t>48,51; 56,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,36; 67,38</t>
+          <t>58,13; 67,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,31; 32,35</t>
+          <t>24,05; 32,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 29,74</t>
+          <t>21,18; 29,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,91; 36,78</t>
+          <t>27,88; 36,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,58; 84,21</t>
+          <t>32,49; 40,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,91; 54,25</t>
+          <t>47,53; 54,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,59; 42,48</t>
+          <t>36,59; 42,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,09; 47,11</t>
+          <t>41,13; 47,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,46; 79,67</t>
+          <t>48,79; 55,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,3; 58,39</t>
+          <t>42,83; 58,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,31; 48,24</t>
+          <t>38,57; 49,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,43; 50,19</t>
+          <t>41,2; 50,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54,26; 66,13</t>
+          <t>52,5; 65,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,54; 33,75</t>
+          <t>23,57; 33,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,97; 43,29</t>
+          <t>35,31; 43,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,9; 43,35</t>
+          <t>34,72; 43,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,06; 51,42</t>
+          <t>43,5; 50,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,35; 39,67</t>
+          <t>31,36; 39,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,21; 43,78</t>
+          <t>37,29; 44,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38,8; 45,21</t>
+          <t>38,54; 44,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,59; 55,07</t>
+          <t>47,6; 53,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,09</t>
+          <t>1,8; 6,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 10,18</t>
+          <t>3,66; 10,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,9</t>
+          <t>1,39; 5,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 8,16</t>
+          <t>2,24; 8,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 24,5</t>
+          <t>19,81; 24,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,82; 27,11</t>
+          <t>21,96; 27,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,1; 26,51</t>
+          <t>20,89; 26,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,44; 29,03</t>
+          <t>22,9; 27,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,55; 20,47</t>
+          <t>16,63; 20,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,92; 23,41</t>
+          <t>18,93; 23,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,12; 22,0</t>
+          <t>17,31; 21,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,88; 23,41</t>
+          <t>18,57; 23,16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,97; 57,2</t>
+          <t>51,76; 57,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,49; 46,29</t>
+          <t>41,64; 46,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,15; 48,56</t>
+          <t>44,05; 48,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,21; 58,7</t>
+          <t>53,52; 58,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,03; 26,51</t>
+          <t>22,95; 26,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,32; 31,03</t>
+          <t>27,12; 31,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,18; 32,11</t>
+          <t>28,33; 32,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,17; 59,56</t>
+          <t>35,32; 38,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,14; 37,24</t>
+          <t>34,04; 37,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34,13; 37,1</t>
+          <t>34,07; 36,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35,77; 38,63</t>
+          <t>35,87; 38,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,64; 60,09</t>
+          <t>43,55; 46,59</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103603</t>
+          <t>116941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>167963</t>
+          <t>190231</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78764; 96407</t>
+          <t>78411; 97148</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57317; 82126</t>
+          <t>58121; 81918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86363; 109841</t>
+          <t>86332; 109484</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90941; 114751</t>
+          <t>105489; 127949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32297; 51438</t>
+          <t>32234; 50594</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27874; 48084</t>
+          <t>27550; 49061</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38563; 62930</t>
+          <t>37698; 62002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55651; 74030</t>
+          <t>62522; 83057</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>114124; 142799</t>
+          <t>114592; 142999</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91427; 125193</t>
+          <t>89727; 123705</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>130865; 164365</t>
+          <t>131116; 164561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>152515; 183052</t>
+          <t>175825; 207091</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107772</t>
+          <t>116743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60682</t>
+          <t>69771</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>168453</t>
+          <t>186514</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68722; 84200</t>
+          <t>68842; 84560</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82283; 108065</t>
+          <t>82341; 109764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67848; 90909</t>
+          <t>66621; 90136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97223; 117378</t>
+          <t>105685; 126319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16991; 36274</t>
+          <t>16943; 36055</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26702; 50597</t>
+          <t>26833; 50258</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27057; 50066</t>
+          <t>27483; 50971</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51691; 69729</t>
+          <t>59695; 79529</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87811; 119951</t>
+          <t>89082; 119512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113662; 154011</t>
+          <t>113162; 151268</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101225; 135795</t>
+          <t>100736; 135623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>154603; 183148</t>
+          <t>172113; 203514</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>143408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>56702</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>182757</t>
+          <t>200110</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>106298; 128777</t>
+          <t>106400; 128086</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>166652; 204788</t>
+          <t>164608; 204985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>158769; 194232</t>
+          <t>157180; 192639</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118570; 141201</t>
+          <t>130557; 155420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14560; 30578</t>
+          <t>13872; 30248</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47696; 72595</t>
+          <t>47130; 71323</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38905; 59531</t>
+          <t>39525; 59410</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43580; 58945</t>
+          <t>48667; 65298</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>122096; 154406</t>
+          <t>123314; 156984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221637; 267624</t>
+          <t>221719; 269045</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202887; 243026</t>
+          <t>203536; 242487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>168151; 195755</t>
+          <t>185269; 215338</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295144</t>
+          <t>321545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>332846</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>627991</t>
+          <t>460723</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>340102; 383378</t>
+          <t>340235; 382722</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>321508; 378406</t>
+          <t>323553; 378097</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>320508; 371897</t>
+          <t>318930; 372838</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>267062; 319316</t>
+          <t>296372; 345529</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>94505; 131149</t>
+          <t>97492; 131547</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97570; 136997</t>
+          <t>97563; 137235</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>126495; 166693</t>
+          <t>126344; 166712</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>196225; 464392</t>
+          <t>124107; 154953</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>446854; 505976</t>
+          <t>443271; 504278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>432550; 502291</t>
+          <t>432629; 500688</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>456380; 523263</t>
+          <t>456797; 524304</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>517364; 816872</t>
+          <t>435081; 491716</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141088</t>
+          <t>150965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>221446</t>
+          <t>242323</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>362534</t>
+          <t>393288</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>70483; 95050</t>
+          <t>69714; 95667</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>132728; 171607</t>
+          <t>137222; 174932</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171762; 213255</t>
+          <t>175051; 215618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127406; 155272</t>
+          <t>135143; 167957</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>83668; 119953</t>
+          <t>83767; 117653</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>201841; 249873</t>
+          <t>203790; 250174</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>186807; 232036</t>
+          <t>185843; 232417</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>204774; 238951</t>
+          <t>224361; 261138</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162471; 205552</t>
+          <t>162510; 205984</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>347177; 408473</t>
+          <t>347887; 411164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>372513; 434095</t>
+          <t>370044; 431952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>339894; 385213</t>
+          <t>368067; 416409</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>197340</t>
+          <t>212714</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>208191</t>
+          <t>223140</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5350; 17974</t>
+          <t>5315; 19334</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9418; 26435</t>
+          <t>9490; 26563</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4139; 16121</t>
+          <t>3801; 15861</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5735; 19412</t>
+          <t>5256; 19368</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>245619; 305757</t>
+          <t>247225; 306632</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>239975; 298189</t>
+          <t>241541; 297921</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>222264; 279182</t>
+          <t>220008; 277909</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>177384; 219656</t>
+          <t>192250; 234540</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>255342; 315866</t>
+          <t>256616; 315594</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257216; 318287</t>
+          <t>257427; 317843</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>227096; 291871</t>
+          <t>229586; 287175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>187757; 232850</t>
+          <t>199395; 248708</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>789584</t>
+          <t>860028</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>928305</t>
+          <t>793978</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1717889</t>
+          <t>1654005</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>704938; 775899</t>
+          <t>702168; 777031</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>820807; 915912</t>
+          <t>823896; 915223</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>856629; 942165</t>
+          <t>854707; 941448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>744637; 837099</t>
+          <t>818737; 902223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>540050; 621747</t>
+          <t>538248; 617994</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>701867; 797363</t>
+          <t>696860; 796496</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>690713; 787195</t>
+          <t>694354; 790635</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>789798; 1265640</t>
+          <t>755512; 829932</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1263898; 1378509</t>
+          <t>1260130; 1369777</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1552310; 1687256</t>
+          <t>1549610; 1680670</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1570645; 1696451</t>
+          <t>1575037; 1707934</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1585293; 2133940</t>
+          <t>1597595; 1709268</t>
         </is>
       </c>
     </row>
